--- a/Topic Relevant Comments/Nigeria/Deyemi Okanlawon_Stop Raping Women Response.xlsx
+++ b/Topic Relevant Comments/Nigeria/Deyemi Okanlawon_Stop Raping Women Response.xlsx
@@ -14,35 +14,17 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="201" uniqueCount="201">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="90" uniqueCount="90">
   <si>
     <t>text</t>
   </si>
   <si>
-    <t>An example of boys being s'xually assaulted and criminal including women:</t>
-  </si>
-  <si>
     <t>YES!!! There is absolutely no excuse and no room for debate when it comes to the safety and bodily autonomy of women. The conversation about ending sexual violence has to start with a clear and loud rejection of the culture that allows it to happen in the first place. This isn't about shifting focus or playing "what about" games; it's about the fundamental right of every woman to live without fear. If we can't agree on this basic truth without adding conditions, we aren't serious about making the world safer for anyone. #EndRape</t>
   </si>
   <si>
-    <t>The rape case that was true at that time nko?</t>
-  </si>
-  <si>
     <t>NO i won't! It's a vague statement that labels all men and only men as rapists. Women rape men too. This evil has existed since the beginning of time. The only real way to reduce it is to build a stronger, fairer justice system that holds all perpetrators accountable.</t>
   </si>
   <si>
-    <t>Women too rape women</t>
-  </si>
-  <si>
-    <t>Lesbian rape is less discussed... end rape.</t>
-  </si>
-  <si>
-    <t>Respectfully, sir. You no get sense!!!!!! 1. What was your contribution when Mirable cried that she was rraped on 15 February and it was a lie? 2. Two days later, a young lady accused David of rape, the police arrested David, and the rest was a story. Later she confessed and apologised that it was a lie. Do you know if it was 10 years ago, Mirable and the lady would have succeeded in accusing men of rrape and those people would be severely punished for nothing??? Sir, what was your contribution to those recent false rape accusers????? I hope that if a lady comes out to accuse you of rrape when you know it is not true, you would be very happy to bear the name RAPIST and all you have worked for taken away from you because of a lie you couldn't prove to be true???? RraPe is a very sensitive topic. So many innocent people have been falsely accused, even when it was consensual, and even though some didn't know anything about it. You can't talk about RAPISTS without talking about ACCUSERS. There are two truths hence they cannot be treated with emotion or gender bias.</t>
-  </si>
-  <si>
-    <t>#endrape yes! But you didn't say anything about false rape accusations? Cause that's literally the issue now! Deyemi are you sure you're man?</t>
-  </si>
-  <si>
     <t>This is a narrative I don't support. Stop raping women, Yes. But when there are alleged rape cases, investigations should be made first to confirm if it actually happened before any slandering, that's my take on this. But we don't do that, instead immediately we hear about rape allegations, we jump into conclusions and start saying things, in so doing, reputations are spoilt, trust is gone, hatred sets in, all manner of things happen afterwards.</t>
   </si>
   <si>
@@ -52,36 +34,21 @@
     <t>But come to think of it. Was it not false accusation that brought this up in the first place. How do we discuss STOP RAP*ING WOMEN, &amp; leave out PUNISH FALSE ACCUSERS, when it's a case of false accusation?</t>
   </si>
   <si>
-    <t>"We need to stop child abuse. What about elder abuse? Domestic violence against women is a serious issue. What about male victims? Police brutality is out of control. What about crime rates?" Lool twitter is not a real place.</t>
-  </si>
-  <si>
     <t>"Stop raping women" is a simple and clear message. I don't understand why there should be a counter. Saying talk about false accusations under every rape case is crazy. Ive not seen women bring up rape cases when false rape allegations is being discussed.</t>
   </si>
   <si>
-    <t>there was a confirmed rape case that happened that week. Quickly explain how her statement isn't still valid</t>
-  </si>
-  <si>
     <t>Yes But Acknowledge RAPE IS BAD first Then Then talk about the false accusations... Replying straight with false accusations almost sound like you are against the "RAPE IS BAD" motion</t>
   </si>
   <si>
     <t>Both events are not mutually exclusive Mr. Deyemi. 1. Men, Do not rape a woman. 2. Women, do not falsely accuse men of rape. There is a possibility of occurrence and non-occurrence when a woman speaks up. From past patterns, it has become neccesary to adopt common sense.</t>
   </si>
   <si>
-    <t>Influential woman is willing to use her power and influence to crush and destroy a poor young boy that was wrongly accused of rape n this is the response of an adult male Poor male child no come live better life for this world</t>
-  </si>
-  <si>
     <t>Okay, the conversation needs to happen—fair, actually very fair. Men shouldn't be falsely accused, and young boys shouldn't be molested either. But why does this conversation only start at the exact moment people are advocating for women not to be raped?</t>
   </si>
   <si>
     <t>Mr A simple "Yes Say No false Accusers " would have prevented all this With the prevalence of false accusations from women these days You cant say you want to speak on rape without condemning the former or atleast acknowledge it when it's brought up That's the situation we find ourselves now, even the case she spoke up for turned out to be another false accusation so telling people to condemn false accusers while speaking against rape isn't asking for too much !</t>
   </si>
   <si>
-    <t>The lies your ilk have been spreading. You not shut people from calling out rapist evening you are one.Rapists will be exposed, whether you chose to focus on false accusations or not.All these rapist,rape apologist and enablers are afraid of being exposed. So they try to deflect</t>
-  </si>
-  <si>
-    <t>What do you have to say about false rape accusations?</t>
-  </si>
-  <si>
     <t>False. When anyone says "STOP RAPING WOMEN" and gets "What about false accusers?", the answer should also be "STOP FALSE ACCUSATIONS." You know why. Stopping false accusers helps us clamp down on rapists faster. So Deyemi, you are VERY WRONG. I understand you're defending a friend, but you didn't do justice to the topic.</t>
   </si>
   <si>
@@ -91,21 +58,12 @@
     <t>80% of the people in the cs are asking "False rape accusation nkor". No one said False Accusations generally is good but why saying it as a counter point to Stop raping Women?</t>
   </si>
   <si>
-    <t>Your reply MUST only be YES. This is how Nigerians use words without understanding the gravity of the words MUST is a strong word you fool. And whenever you also hear of rape the accused and the accuser also have right to prove their innocence or guilt there's no must it is observing the situation and bringing proof enough of false accusations and using the woman deception when you say rape let it be rape and women should stop going to men houses she should request for an open space enough of them also putting themselves in a position that can trigger a raping instinct.</t>
-  </si>
-  <si>
     <t>But with that simi tweets, having sexual fantasy about children, will you use this same energy and do us a very big favor by putting out "STOP MOLESTING, RAPING OUR CHILDREN"? Some of you hopeless horny badgers calling yourself men, are the reason innocent boys have no say when they being abused, sexually molested, raped by the likes of simi. The same you will want to tell your son to man up when a girl who lacks home training abused him. But you can't even tell the damage that will cause him because you're a useless man who shouldn't have a say when it comes to public opinion. The same you will be in approve of how those grown men become a rapist, which only gives you blast headache when they get caught, but you will go mute when a female rapist, a female pedophile is being apprehended in her child molesting character. Better no carry this foolish mentality and speak in public, or you won't be the one who return home. Oloriburuku, Oponu.</t>
   </si>
   <si>
     <t>I know what you are. You can fool yourself but not me. If a rape case is brought up with only words of mouth, we won't rush to condemn without evidence. The person must be found guilty before we condemn. It's simply the law. There are possibilities of false rape accusation and we can't condemn an innocent person, their blood won't be on my head. We condemn all rapist and false rape accusers irrespective of their gender once they're found guilty. Rape is Evil and so is False Rape Accusation. If you condemn when the victim is a woman and keep quiet when the victim is a man, you're not just and you're a hypocrite. Proverbs 18:13 AMPC [13] He who answers a matter before he hears the facts–it is folly and shame to him. [John 7:51.] John 7:51 AMPC [51] Does our Law convict a man without giving him a hearing and finding out what he has done?</t>
   </si>
   <si>
-    <t>What if you're being accused of rape falsely, is it this rubbish you'll be saying ‍♂️??</t>
-  </si>
-  <si>
-    <t>Why will I say YES when I didn't engage in rape or any sexual crimes? This is a very dumb thing to say. It's as Dumb as those men that engage in sexual crimes.</t>
-  </si>
-  <si>
     <t>Just from 2025 till this very moment, are you ignorant of the number of false rape accusations that has been recorded? Will you pretend you don't know what it does to the victims? Didn't you hear about the Enugu man that was accused of abusing his twin daughters?</t>
   </si>
   <si>
@@ -121,9 +79,6 @@
     <t>U r just repeating what the original tweet spoke against. When someone speaks against rape your first response shouldn't be what about false accusers but should be in support of victims cos rapist actually live among us. It's like asking what a woman wore after being raped.</t>
   </si>
   <si>
-    <t>Oga, you are a rapist! Stop raping women. I expect you to say yes sir. #Ezì</t>
-  </si>
-  <si>
     <t>No There was an original rape case (Fems and her friend), before Mirable brought hers Even if there was context it isn't about false accusations But then she didn't mention any case on her tweet She only said "stop raping women"</t>
   </si>
   <si>
@@ -133,66 +88,36 @@
     <t>Stop raping women" isn't a question that needs a response; it's a standalone statement. Asking a follow-up question in the same context about rape "What about false accusers?" is a valid question. Responding to such a harmless, sensitive, and genuine ques with "stfu" is stupid.</t>
   </si>
   <si>
-    <t>Look at this low quality omah lay telling me to accept Rape accusations, if you are a rapist "if" doesn't make Everyman a rapist. Accept it when it's your call of duty not mine</t>
-  </si>
-  <si>
     <t>This is why I don't rate celebrities above what they are—humans. Stop rap!ng women, valid. Your dixk don rise. We never hear nor see you when young boys are speaking about how they were molested by older female adults. We never hear you when men are accused of r falsely. With no due respect, stfu. Both conversations are important.</t>
   </si>
   <si>
-    <t>You won't force her to divert....she was standing on rape itself and wasn't done with that,and it is irrational to comment shut under that tweet...the percentage of false accusation is 2 and not a main topic at that time...y'all grow up</t>
-  </si>
-  <si>
     <t>Some of you really need to research before speaking. She said 'stop raping women.' Someone tried to shift it to false accusations, and she stayed on topic. That's not persecution that's focus. Bringing up false accusations in that moment does it even make sense? please answer???</t>
   </si>
   <si>
-    <t>There's no human on earth who had agreed to rape You all are just devil and you do look like who would accuse someone of false rape with that your forehead like ninja turtle That girl should be serving term now but she's not fuck you all miserable lot</t>
-  </si>
-  <si>
     <t>Lets stop acting blind and bias please. In as much as you're right, there's context and deep history in this particular subject. People on this app didn't just wake up overnight and start trying to speak up and ask questions about "False Rape Accusers". Is a crime that has been going on for yearssss now. People have died, men have unalived themselves, lost jobs, opportunities, contracts, families, friendships etc over false rape accusations. So whenever there's a rape case... People want to make sure it is true or false. So if you decide to speak about rape... You should equally speak about the other side of it. On our very eyes some group of women came together with bitterness and formed an evil coven called "feminist" ... every week on this app they were falsely accusing guys of abuse and rape. Nobody spoke up.. not a single celebrity spoke up.. And that's how the likes of Shola, Wiz, Neo etc came up and start speaking up regardless if you agree to some of their takes or not. Also... Simi has been doing this for years.. right since 2023. She's always trying to pretend like she's fighting for a good course ONLY when it involves a Woman. When is a Man on the victim side.. She goes silent. Everyone has clocked her. So let nobody try to be a moral police now. I have seen Men on this app drive away abusive and useless men. People like Kelvin Odanz can't come to this app again. Nobody is saying Simi shouldn't fight against Rape... actually, the penalty for rapist should be life in prison or hanging. But if you must fight for true course... COME CORRECT AND TRUE. That been said.... Why is the Mirabel girl and the other girl who also accused a poor boy that was arrested same week not yet in Police Custody? Now, imagine if the truth didn't come out and she actually pointed at a guy on her street. Imagine!?!?</t>
   </si>
   <si>
-    <t>Something I don't understand y'all So it is ok when someone talks about false rape accusers and I reply with "what of rapist"</t>
-  </si>
-  <si>
     <t>Let's address your statement, Mr. Adeyemi. "Your reply MUST only be YES!!!" This is in a situation where all the men reading her posts are rapists. Not all men are rapists, and all rapists deserve excruciating d*ath. Secondly, why weren't you in the comment section that day to type your "YES!!!"? Thirdly, when she was lending her voice to speak for women, I believe the person who asked about false accusers wanted her to speak on that too. "STFU" isn't the best way to address it. Lastly, rape and false accusations must both be eradicated, and being biased won't bring the change we want. Peace ✌</t>
   </si>
   <si>
     <t>Fuck, am I seriously having to explain basic reasoning to u?I'm disappointed. No normal person should be fine with rape,the word alone should repulse any real man.But we still have to know when to distinguish between an actual rapist, a pedophile,and a false accuser. WAKE UP !!!</t>
   </si>
   <si>
-    <t>Coming from Simi that loves to start gender wars that question needs to be asked And false rape accusations shouldn't be suppressed except you're just pandering to your female audience So when will they talk about "False Rape Allegations?" After 14years jail time? Get out you</t>
-  </si>
-  <si>
     <t>Why should the individual be telling her to speak on false accusations when the topic was rape?</t>
   </si>
   <si>
     <t>Don't mind Nigerians they want use Simi's old tweets of about 20 years ago against her just because she choosed to use her influence and social media platforms to speak-up against the high level of sexual violence, rape and sexual abuses that alot of ladies face in our society today. Our young girls and women has been sexually objectified in the society and most of them has been reduced to objects of sex abuse in all the sectors and corners of the country. • Our women and girls can't seek for employment opportunities and get it here in this country without taking advantage of them. • Our women cannot seek and get promotions in their different places of work without mandating to compromise sexually. • Our women and girl's can't get good grades for their different schools without asking them to compromise sexually.</t>
   </si>
   <si>
-    <t>After the end of the day, that current trending r*pe case is a false accusations... What do you have to say about that?</t>
-  </si>
-  <si>
     <t>It would have been a different thing if the rape on mirabel had been confirmed before she posted "stop raping women."</t>
   </si>
   <si>
-    <t>Even if it comes from a rapist, yes it still remains and she didn't molest any child, no amount of crying will change that all bcos someone told you all not to rape, my God will continue to purnish all of you and I hope she makes one if you a scape goat, idiot</t>
-  </si>
-  <si>
     <t>I beg to disagree sir. When you talk about rape case. You gats to talk about everything surrounding it. Including false accusations</t>
   </si>
   <si>
     <t>It's easy for you to come with such context. You will know how bad and damage it is to falsely accuse someone of rape if it happens to someone you are close to...</t>
   </si>
   <si>
-    <t>Just pray someone doesn't accuse you of rape, our answer will be YES.</t>
-  </si>
-  <si>
-    <t>Thank you Deyemi School all them rape apologists!!</t>
-  </si>
-  <si>
-    <t>"Raping women" is indirectly calling all men rapist. Now tell us, how many men from your family has raped women before? Also how many women from your family has being raped before?</t>
-  </si>
-  <si>
     <t>"YES" is the only reasonable response to "stop raping women." Nobody is arguing against that. But let's not twist the situation, no one said men should rape women. That's a false framing of what actually happened. The issue was that she shut down people who were simply asking questions to make sure the accusation wasn't false. That's not defending rape that's asking for due process. And as we now know, the accusation turned out to be false, which proves why scrutiny matters. If you want to carry water for her, at least stick to the real context. Acting like anyone who asked for evidence was encouraging rape is manipulative and dishonest. Supporting victims does not require silencing questions or abandoning fairness.</t>
   </si>
   <si>
@@ -202,9 +127,6 @@
     <t>Why are this stupid Broo No one is defending rapist here. But do you know how many of your black brothers have been rotting in jail because of rape accusations. Do you know how many lives have been damaged because of rape accusations Do you know how family have been torn??</t>
   </si>
   <si>
-    <t>Don't worry Deyemi, when they accuse you of rape, we will believe the accuser without evidence</t>
-  </si>
-  <si>
     <t>When anyone replies, "What about false rape accusers?".. your QT should either be that they get punished or you don't reply at all. Quoting such a serious case with "Stfu" is you starting a seperate conversation of invalidating victims of such.</t>
   </si>
   <si>
@@ -217,12 +139,6 @@
     <t>Whats famous is rarely wise. The conversation is not about rape. The rape issue was alleged to be false, confessed by the said victim. The issue on the ground is Simi exhibiting paedophilic traits. What is your comment on that?</t>
   </si>
   <si>
-    <t>All the men don't have to be rapist to agree to a good request/plea na</t>
-  </si>
-  <si>
-    <t>One day the false accusations will reach your door step, you will look for people to defend you and all you will find is angry feminists.</t>
-  </si>
-  <si>
     <t>You are free to create a separate post about false accusations. What you cannot do is dictate that someone discussing rape must include your preferred topic. That does not make sense. If a statement condemning rape triggers you more than the crime itself, then you have a problem.</t>
   </si>
   <si>
@@ -238,9 +154,6 @@
     <t>Being economical with the truth doesn't make you intelligent. We all know the full context of her tweet. You can't clamour for rapists to be punished while refusing to reckon with false accusations. Both are crimes, and they're mutually exclusive. I wonder how some of you think?</t>
   </si>
   <si>
-    <t>But you know she could have condemned "false rape accusations "even at the heat of the whole rape stuff amd still stand well rather than trashing it. Sha na women thought process</t>
-  </si>
-  <si>
     <t>The rape case she was speaking out for was later confirmed to be false. Now what does that tell you? I wonder if you guys calm down and think.</t>
   </si>
   <si>
@@ -253,315 +166,99 @@
     <t>Deyemi,you've set yourself up for dragging. We see people who towed this path here &amp; how they became victims,their grammar changed. I guess you have 2 or 3 Sons,you should be the championing the need for punishing false rape accusations while kicking against rape too. Don't pander!</t>
   </si>
   <si>
-    <t>Saying stop the graping women under a false rape accusation trend is stupidity!</t>
-  </si>
-  <si>
-    <t>Guys like you are the rapists in reality.</t>
-  </si>
-  <si>
     <t>Aren't we humans? Why are we acting like we are incapable of simultaneously conversing on multiple topics surrounding the same subject. We can talk about holding men to better standards AND at the same time talk about putting an end to false accusations, the end goal for both discussions is to eradicate rape culture. Both conversations are not so mutually exclusive that they must be had at separate times.</t>
   </si>
   <si>
-    <t>How about she just respond "yes false rape accusers should face capital punishment" why was she triggered that rape accusations could also be false?</t>
-  </si>
-  <si>
-    <t>Deyemi, go warm eba jare. You're saying nonsense. You won't decide how we respond to people of questionable character on this app. Who made you a judge sef? If you say "stop raping women", my response would be "stop raping women, men and kids". Rape knows no gender.</t>
-  </si>
-  <si>
     <t>It's 2026 we can't be this naive! We've seen a lot gone wrong with not asking questions where men been put in jail under false accusation cause people only wanted to look at one side of a story. We can't turn a blind eye to the high statistics of false accusations cause we are not allowed to ask questions. No we have to ask questions, we have to gather facts, we have to support yet not be naive and bias. Because people only realise it is important to ask questions only when shiii hit home, when it is your kid or brother or any of your loved ones being accused of such. Gather facts from all sides.</t>
   </si>
   <si>
-    <t>I stopped reading your piece of nonsense at "choosed". When they falsely accuse you of rape, we will not speak out for you</t>
-  </si>
-  <si>
-    <t>Exactly... I respect your honesty. I wish more men will think like you</t>
-  </si>
-  <si>
     <t>Man,you are probably well educated but you just veered off the whole context of the conversation, and I can question that the education did not pass through you. Nobody agreed to men raping women but should we just take the accusers word for it when we know false accusation exist. Better pray make e no reach your side</t>
   </si>
   <si>
-    <t>She is within her right to shut them up! Go and start your new conversation about false accusations on your page. List out the number of men you can swear with your lives were falsely accused, then list the number of girls/ women you can swear were raped. Don't be stupid</t>
-  </si>
-  <si>
-    <t>Okay, lets agree with you. Can you now comment on the grave issues surrounding her past tweet? Or are you claiming not to see them? When you stand up for the boy child?</t>
-  </si>
-  <si>
     <t>I don't understand why some people think people(women) can't lie and architect an innocent man's downfall, the double standards are glaring</t>
   </si>
   <si>
     <t>She was right to say STfU, you shouldnt be addressing false accusations when the topic is rape, imagine if people started making it about rape when the news of that uni guy who was falsely accused and committed suicide broke out</t>
   </si>
   <si>
-    <t>If I talked about false rape accusers and asked for heavy inhumane punishment on them and someone commented and ask me what about rapists. Then I replied with "STFU". Will you be saying this same thing in my defense. Adeyemi, you are a fool among many other things.</t>
-  </si>
-  <si>
-    <t>Bingo The response was for proper verification of the allegations and she responded with stfu. Give birth and wait for someone to acuse your own child first, maybe then you'd truly understand the damage of false rape accusations.</t>
-  </si>
-  <si>
     <t>You better come correct before you collect. This narrative was not how it happened. Simi did not say "stop raping women" Simi said "castrate all rapist" and someone said "let's add false rape accusers too". And she replied "STFU" Better know matter before you jump in</t>
   </si>
   <si>
-    <t>This same you have never advocated for "stop false rape accusations" shows clearly whom you are.</t>
-  </si>
-  <si>
     <t>Really? So tell me, what's so bad in discussing both the topic of stop raping women and stop false accusations at the same time? Her response saying stfu, was the main trigger to her being dragged like this. Don't you think it would have been easier to just discuss it all?</t>
   </si>
   <si>
-    <t>So, who is stopping you from taking action against what the guy did? If he is found guilty, he should face the consequences of his actions. Stop this fooling you are doing fgs</t>
-  </si>
-  <si>
     <t>There was an accusation. If false, it can destroy a man's life. On this same app, there are women who confesses to use false accusation as a weapon. On this same app, we read about false accusation. With an accusation on ground, ...</t>
   </si>
   <si>
     <t>It can't come up in a different argument. You can't separate both. Don't you get it. If there is an accusation of being rape, then there's also a possibility of it being false. That's where the investigation come it. You don't just believe hook line and sinker without trying to process the story being told. This doesn't mean you shouldn't show sympathy to the supposed victim. Give her a listen ear, show sympathy and concern, but at the same time be open to the possibility of it being false. That's all we are saying.</t>
   </si>
   <si>
-    <t>The case turned out to be false.. Simi said stop raping women Another person said what about false rape accusers Then simi said STFU... But bcus of the kind person wey you be, you no fit understand</t>
-  </si>
-  <si>
-    <t>You can't force your opinion on people by saying stop raping women, you don't like that opinion?</t>
-  </si>
-  <si>
-    <t>Deyemi that moment she made that tweet was attached to a false accuser of rape and you know it . Sometimes make una dey use una sense, set your emotions aside and don't be sentimental. She could have just made a tweet about the false rape shi that won't even take 10 secs</t>
-  </si>
-  <si>
     <t>Did he lie? If the conversation is about Raping women, why are you bringing up false rape accusers? If you want to talk about False rape accusers pick a day and talk about it.</t>
   </si>
   <si>
     <t>This is like saying: After an accusation, right or wrong, without knowing, and wanting to know the truth of it, an Influencer can start a campaign on "Stop making false rape accusations" In both cases, the campaigns are good but insensitive to the truth, or the search of truth</t>
   </si>
   <si>
-    <t>You wey be actor, that career wey you hold dearly, one false accusation could ruin it to the ground sha, hope you know? And yet you're saying false rape accusation and rape shouldn't be in the same conversation. Time would tell</t>
-  </si>
-  <si>
-    <t>You mock our brothers who are languishing in prison based on false rape accusations. I hope some day, you get 5 women falsely accusing you of raping them. Then you can come and post this shit after coming back from serving a 30-year stretch. You should have been in Thomas Partey's shoes without Thomas Partey's money to hire good lawyers. That's when we would be able to see how smart you really are.</t>
-  </si>
-  <si>
-    <t>We will be here when one of the Olosho actress will accuse you of rape that happened in 1998 just to destroy you, we go gather support her. We will do go-fund me just for you to enter prison. Continue running after pumeme.</t>
-  </si>
-  <si>
-    <t>A witch who accuses innocent men of false rape is talking about contradiction?</t>
-  </si>
-  <si>
-    <t>Nobody disputed her that in short more than half of the people in her CS agreed with her, just few people asked "what about false rape accusers" then her response was STFU and una dey cry like say you don't know what really cause the issue Make una dey Mumu dey go</t>
-  </si>
-  <si>
     <t>I get where you are going. But telling people to just say "yes" and never question anything feels off. Real justice needs truth and due process. Not pressure to stay silent. If people are afraid to ask questions, that's not accountability anymore.</t>
   </si>
   <si>
-    <t>You guys act like there was no context to that tweet, what was trending at that time was a lady who lied abt raped</t>
-  </si>
-  <si>
-    <t>Man y'all are morons tbh. So you agree you can't force your opinion on others but Simi should be forced to accept you people's opinions? Point us to where anyone has advocated for false rape accusers, please.</t>
-  </si>
-  <si>
-    <t>Someone came to accuse all men of being rapists siting a story she didn't bother to assess how true it is. Everyone with a working brain could tell the girl was lying. But that didn't matter to her. She just wants to accuse all men of being rapists including her husband and her father. She is brainless. And by telling us what our reply MUST be to her stupid statements, you as well are equally BRAINLESS. A really good actor but still BRAINLESS.</t>
-  </si>
-  <si>
     <t>Also, false accusers are more dangerous because they reduce the possibility of real victims getting justice by the day. More women will be afraid to speak up if you don't deal with false accusers.</t>
   </si>
   <si>
-    <t>Were you happy the way the police treated him? The public ridicule, etc Did you not hear about Izuu that took his own life for the same false rape accusation? Will you bring him back to life? Can you now see that you're a big fool? You and your type are animals!</t>
-  </si>
-  <si>
     <t>It's the fact that you think we all don't agree with the yes. Yes yes yes. Stop graping anybody. Okay, can we discuss false accusers? No. That's not what we're discussing. Really? Graping and false accusations are two sides of the same coin. You can't simply flip the coin again because the side facing up is "false accusations." You can't just keep flipping until you get an actual "grape" incident. That's the discussion. And the story aged really fast. The story she was defending turned out to be false. The coin landed with the side she didn't want to discuss. You wanted a yes to her statement. How about a yes to the other side now?</t>
   </si>
   <si>
     <t>"Yes" should be the correct response....you are absolutely right. In the case of whataboutism.... She should have said she should have yes to "no to rape accusation"... As a celebrity, you should learn to meet your fans at different level of questioning... outrightly saying stfu wasn't a good response. Also, 2 truths can co-exist and the line of questioning for a what-if or what about question is to get anyone.... and she just sadly feel for it....</t>
   </si>
   <si>
-    <t>Your reply could be 'YES' and a question about false rape accusers. Don't try to play like Pique for Simi. You also align with her old tweets?</t>
-  </si>
-  <si>
-    <t>I have always known you are a dullard and a stupid fellow thats why i skip ur foolish movies. Just look at what someone that calls himself a ma wrote here? Do you think we too support rape? All i am saying is keep same energy when its time fo4 false accuser, you are here blabbing rubish.</t>
-  </si>
-  <si>
     <t>Ignore this one,he knows what he is doing jare. Until he is a victim of false accusation or someone close,he will not understand.</t>
   </si>
   <si>
-    <t>It's alway the faceless accounts that come here to make dumb statements. Simi is married to man and yet she said "all men are rapist" your stupidly is very loud ode Oponu oshi</t>
-  </si>
-  <si>
-    <t>This conversation started because of Mirabel who was later proven to be lying thanks to people who asked that question that you don't want people to ask</t>
-  </si>
-  <si>
-    <t>You have sons, I hope and pray they don't get into sick situations And I hope and pray you maintain this opinion that time</t>
-  </si>
-  <si>
-    <t>This man you need read this ooo so you go rethink your logic aswr</t>
-  </si>
-  <si>
     <t>Wasn't the whole write-up prompted by the issue of false accusations? So how was his question not valid? Asking a question is not a crime that deserves a "shut the fuck up." A respectful discussion should be met with a respectful response, not insults.</t>
   </si>
   <si>
     <t>How can a woman be this logical than a man? please they should stop generalizing all women as being incapable of logical reasoning cos a lot of men like the he-goat who quoted simis tweet have proven over time that some women are smarter than men</t>
   </si>
   <si>
-    <t>Is that how it started?? E no dey hard to identify man wey dem don use toto water cook for. Furthermore the case for which she was barking like a wild rabid dog for turned out to be false but i guess you have no idea how many innocent men are rotting away in jail due to that.</t>
-  </si>
-  <si>
     <t>True! In as much as false rape accusations is punishable offense, that can come up in a different argument. You all Twitter users always want to act like you're smarter than all. Simi message was simple. But Twitter users?? They changed the entire conversation.</t>
   </si>
   <si>
-    <t>Bro. You no talk about your fellow man they accused of false allegations oo? Buh uno matter sha</t>
-  </si>
-  <si>
-    <t>You're right, that was were simi outrage began mumu people on here with low understanding was just dragging her ndi ara</t>
-  </si>
-  <si>
-    <t>Empathy when the case is false? If we acted on emotions you'd prosecute an innocent man. I'm sorry to say this you're a fool</t>
-  </si>
-  <si>
-    <t>I used to respect you, but this your take is trash</t>
-  </si>
-  <si>
-    <t>"DON'T THINK ABOUT HOW LITTLE SENSE IT MAKES JUST SUPPORT THIS SHITTY ACCUSATION" No.</t>
-  </si>
-  <si>
-    <t>This energy! Awe! I wish I never married! .I for take you home! Thank you for speaking sense into him. How can a grown man lose his sense all because he wants to lick toto? Forget common sense! Each time he opens his mouth, he's even stupider than the stupid girl in question</t>
-  </si>
-  <si>
-    <t>Thank youuuu!!!!!!! Twitter men's response to "stop r women" is always another thing Na God go take all these banger boys</t>
-  </si>
-  <si>
     <t>You no too get sense. E don tey we know. The reason people are talking about those who were accused falsely is because people like Simi have the platform to amplify such positive narratives. The handles that asked the question don't have many followers like her hence, they posed the question to her. All Simi could do is show some grace and empathy. "False accusers deserve to be condemned and punished, however, let's focus on the case at hand." Yemi abi wetin them call you again, STFU!</t>
   </si>
   <si>
-    <t>Deyemi with all due respect STFU. If we're talking about an action, it's perfectly okay to still talk about the reaction.</t>
-  </si>
-  <si>
-    <t>Why should that be your first response? That is not my first response jor, I will never be part and parcel of incriminating and innocent man.</t>
-  </si>
-  <si>
     <t>You have a point. But where she got it wrong was being vulgar when someone asked what about false r accusations. She couldn't have just ignored the tweet rather than typing STFU. Meaning I don't F care about that. You know false r accusations is a big deal.</t>
   </si>
   <si>
-    <t>When ur time come we go Dey here weak man na Una be enabler</t>
-  </si>
-  <si>
-    <t>"Yes" is implied in that response She could have then replied: "and that too" Don't you think so Deyemi?</t>
-  </si>
-  <si>
-    <t>All the werey wey dey talk rubbish, if them accused them of gr and the allegation na false, na that time explanation about false accusations go full their mouth. But before then, rubbish na him dem go dey talk.</t>
-  </si>
-  <si>
-    <t>Is that most of you didn't see that she did shut that guy down by saying "StFu" and then she went on to explain herself on why ?</t>
-  </si>
-  <si>
     <t>She shut it down cos that was not the conversation nor was she addressing false accusations. There is something they have dropped in the water in that Nigeria that got your arguing over something as simple as this. You're tone deaf and painfully arrogant. Dang!</t>
   </si>
   <si>
-    <t>If you cast, drop evidence too. Otherwise we go wave am away as false accusation</t>
-  </si>
-  <si>
-    <t>What is this one saying again? Can you read what you just tweeted? VERY WRONG oga deyem!</t>
-  </si>
-  <si>
     <t>You are totally wrong! Why did your friend that you came here to defend not just reply "yes" about false accusers but instead tried to silence someone who innocently asked her about false accusation? Can't you see you're just the same hypocrite and an unjust fellow?</t>
   </si>
   <si>
     <t>Simple and short. I don't know what's going on with Nigerians. There are so many aspects to a conversation. Choose yours and let others choose theirs.</t>
   </si>
   <si>
-    <t>Alaye! Respectfully,you too don't have sense. You know Mirabel case has almost successfully been sweep under the carpet but it's Simi receiving the bullets now. No go carry another person war for head óò!</t>
-  </si>
-  <si>
-    <t>Hurts me so much when I see people I actually idolize turn out to be morons, I thought this guy was a smart guy until I came across this tweet. You could have just kept quiet mehn.</t>
-  </si>
-  <si>
-    <t>This man go make people go dig up him own past o</t>
-  </si>
-  <si>
-    <t>Vee there is absolutely nothing to drag here, we just like dragging rubbish. the guy is absolutely right.</t>
-  </si>
-  <si>
-    <t>God bless you, because I don't understand the madness on my timeline</t>
-  </si>
-  <si>
-    <t>Stop raping women</t>
-  </si>
-  <si>
     <t>The person simply wanted her to apply logic &amp; critical thinking, just as this person here has done. For a matter of that magnitude (that ended up to be false), logic &amp; critical thinking are actually very important. It's worrisome that we have to explain these things to you guys.</t>
   </si>
   <si>
-    <t>she was the rapist</t>
-  </si>
-  <si>
     <t>Thank you! All of them know what they are doing,they want to silence people from speaking up against abuse. Hell to rapists and their apologists!!!</t>
   </si>
   <si>
-    <t>You are a rapist. Stop raping women.</t>
-  </si>
-  <si>
     <t>Thank you uncle actor. #Endrape We should learn to be contextual</t>
   </si>
   <si>
-    <t>Deyemi, stop raping women.</t>
-  </si>
-  <si>
-    <t>Deyemi STOP rap*ng women.</t>
-  </si>
-  <si>
-    <t>Then we address that and call for the arrest of the false r*pe accuser.</t>
-  </si>
-  <si>
-    <t>Uncle Deyemi we have since moved past "stop raping women" We all agree to that statement, right now we addressing Simi's child sexualisation tweets.</t>
-  </si>
-  <si>
-    <t>"Stop raping women" wasn't the tweet that caused outrage. Research and find out.</t>
-  </si>
-  <si>
-    <t>You were probably sexually harassed/molested as a kid, and you're here opposing the voices speaking up for children that MAY have experienced abuse?. You're evil.</t>
-  </si>
-  <si>
-    <t>So you are now conditioning people on how to talk about about r^pe and its associated cases because Simi is involved? When men who are supposed to make a decisive statement keep pandering and egging women's emotions, you just know he's performing for a crumbs of p#ssy</t>
-  </si>
-  <si>
-    <t>E no dey hard to detect feminine men END FALSE R^PE ACCUSATION</t>
-  </si>
-  <si>
-    <t>Stop defending perverts. There is no law or rule that specify when to call out one crime over another. #HangTheRapists #HangThePedophile</t>
-  </si>
-  <si>
     <t>Exactly! Anything after that is goading the poster and undermining their personal experinec3s and the tru import of their message. You can also make a post on your own perspective.</t>
   </si>
   <si>
-    <t>As how? "Your reply must only be YES" keh What's with the generalization? All men are not rapists, no dey wurungbon lenu abeg</t>
-  </si>
-  <si>
-    <t>Simple. That's d point a lot of these men missed Most of them are guilty of SA</t>
-  </si>
-  <si>
-    <t>That's why he said start your own conversation about that but stop raping women</t>
-  </si>
-  <si>
-    <t>Why will my answet be yes If I have never raped a woman in my life?</t>
-  </si>
-  <si>
     <t>Justice requires both compassion for the accuser and fairness to the accused. An investigation is not a dismissal of a claim; it is the pathway to truth.</t>
   </si>
   <si>
-    <t>With men everything is a competition unfortunately.</t>
-  </si>
-  <si>
     <t>this is your jargon. Many ladies i knowget good grades in universities, top their departments, get jobs and also get promotions without being sexually exploited. Maybe your women are the mediocres that offer sex for some of these things, definitely not OUR women</t>
   </si>
   <si>
     <t>Thank you for understanding the tweet and speaking up. They literally changed the whole narrative to suit their agenda.</t>
   </si>
   <si>
-    <t>If you say "Yes" it only means you are that you are a grapist and agree to have graped someone in your past or present. You cannot say "Yes" when someone else is infact the grapist. Saying "Yes" means you agree that you are a "Grapist". This has nothing to do with the accused.</t>
-  </si>
-  <si>
-    <t>You're right, the backlash has just been absolutely unnecessary</t>
-  </si>
-  <si>
-    <t>A lot of ladies? How many false accusers have we seen in the past years compared to actual rapists? You people are brainless.</t>
-  </si>
-  <si>
-    <t>Listen fool, the conversation has now shifted from stop raping women to Simi being a pedophile and a possible rapist. That's the conversation we're having now. So idiot, is Simi a pedophile? Your reply MUST only be YES or stfu</t>
-  </si>
-  <si>
     <t>I believe everyone has the liberty to stand for what they believe, no one has ever denied "Stop r^ping women" but what you refuse to understand is that they are refusing to agree to persecute false accusers . Also you can't force your opinion on people Know this and know peace</t>
   </si>
   <si>
@@ -571,46 +268,16 @@
     <t>This is how hypocrites are being checkmate. You cannot be a predator, child molester and rapist yourself and still be a leading voice for women against molestation and abuse.</t>
   </si>
   <si>
-    <t>Stop r women!</t>
-  </si>
-  <si>
     <t>"Your reply must be yes," and after saying yes, what's next? Should we not talk about the other aspects of this terrible crime? Should the response of sharing awareness of it be "stfu"? Why are you being stupid deyemi. With no blue tick too. Just being dull for the fun of it</t>
   </si>
   <si>
-    <t>"Absolutely right" = in YOUR books</t>
-  </si>
-  <si>
-    <t>Well I support this</t>
-  </si>
-  <si>
-    <t>Thank you for this you are right. Now I want to start it here women should stop accusing men falsely.</t>
-  </si>
-  <si>
     <t>Must be a fool to think it's in your place to tell men how to respond to these things. You know very well why these topics are being discussed you know why these dialogues are happening.</t>
   </si>
   <si>
     <t>You've been on this app since 2009 and that's long enough for you to understand why men are also asking her to lend her voice to both instances because they go hand in hand. If I say, "Stop false r accusations against men" and someone asks me "what about r women?", I'll also say "Yes, stop r women too" because both are as bad as it can get. But because we are emotional beings instead of being concerned about ourselves, we tend to be insensitive and when you tell people to "stfu" it means you do not care so therefore people will react too. She had the platform to have also made that statement, nobody is ignorant about that. So Deyemi, think about it.</t>
   </si>
   <si>
-    <t>We can't talk about r and not talk about false r accusers. NO WAY!!!</t>
-  </si>
-  <si>
     <t>When someone says; what about men ? Your response shouldn't be STFU, it should be "including men and children" Ire oo</t>
-  </si>
-  <si>
-    <t>How about we talk about pedophiles</t>
-  </si>
-  <si>
-    <t>Big Love I so much love how you stand behind women. God bless you</t>
-  </si>
-  <si>
-    <t>That stupid empathy would've transferred to David's case &amp; ultimately ruin him as we speak if someone had not interrupted the negative energy What's even wrong with all of you. So because she's a WOMAN means we can't say anything whenever she's wrong, abi kini gbogbo werey yi na</t>
-  </si>
-  <si>
-    <t>What should be the reasonable reaction to this?</t>
-  </si>
-  <si>
-    <t>Very rubbish take. So because someone makes an accusation, we should just agree? Did they pay you to tweet this rubbish</t>
   </si>
   <si>
     <t>I understand this defense but not to think of men when women say ## is unarguably and in this case it was FALSE still yet proven. U Dey find different conversation when it's all in same premises</t>
@@ -974,7 +641,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A201"/>
+  <dimension ref="A1:A90"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:1">
@@ -1427,561 +1094,6 @@
         <v>89</v>
       </c>
     </row>
-    <row r="91" spans="1:1">
-      <c r="A91" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="92" spans="1:1">
-      <c r="A92" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="93" spans="1:1">
-      <c r="A93" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="94" spans="1:1">
-      <c r="A94" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="95" spans="1:1">
-      <c r="A95" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="96" spans="1:1">
-      <c r="A96" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="97" spans="1:1">
-      <c r="A97" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="98" spans="1:1">
-      <c r="A98" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="99" spans="1:1">
-      <c r="A99" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="100" spans="1:1">
-      <c r="A100" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="101" spans="1:1">
-      <c r="A101" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="102" spans="1:1">
-      <c r="A102" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="103" spans="1:1">
-      <c r="A103" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="104" spans="1:1">
-      <c r="A104" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="105" spans="1:1">
-      <c r="A105" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="106" spans="1:1">
-      <c r="A106" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="107" spans="1:1">
-      <c r="A107" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="108" spans="1:1">
-      <c r="A108" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="109" spans="1:1">
-      <c r="A109" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="110" spans="1:1">
-      <c r="A110" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="111" spans="1:1">
-      <c r="A111" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="112" spans="1:1">
-      <c r="A112" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="113" spans="1:1">
-      <c r="A113" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="114" spans="1:1">
-      <c r="A114" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="115" spans="1:1">
-      <c r="A115" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="116" spans="1:1">
-      <c r="A116" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="117" spans="1:1">
-      <c r="A117" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="118" spans="1:1">
-      <c r="A118" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="119" spans="1:1">
-      <c r="A119" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="120" spans="1:1">
-      <c r="A120" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="121" spans="1:1">
-      <c r="A121" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="122" spans="1:1">
-      <c r="A122" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="123" spans="1:1">
-      <c r="A123" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="124" spans="1:1">
-      <c r="A124" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="125" spans="1:1">
-      <c r="A125" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="126" spans="1:1">
-      <c r="A126" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="127" spans="1:1">
-      <c r="A127" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="128" spans="1:1">
-      <c r="A128" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="129" spans="1:1">
-      <c r="A129" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="130" spans="1:1">
-      <c r="A130" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="131" spans="1:1">
-      <c r="A131" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="132" spans="1:1">
-      <c r="A132" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="133" spans="1:1">
-      <c r="A133" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="134" spans="1:1">
-      <c r="A134" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="135" spans="1:1">
-      <c r="A135" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="136" spans="1:1">
-      <c r="A136" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="137" spans="1:1">
-      <c r="A137" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="138" spans="1:1">
-      <c r="A138" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="139" spans="1:1">
-      <c r="A139" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="140" spans="1:1">
-      <c r="A140" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="141" spans="1:1">
-      <c r="A141" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="142" spans="1:1">
-      <c r="A142" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="143" spans="1:1">
-      <c r="A143" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="144" spans="1:1">
-      <c r="A144" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="145" spans="1:1">
-      <c r="A145" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="146" spans="1:1">
-      <c r="A146" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="147" spans="1:1">
-      <c r="A147" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="148" spans="1:1">
-      <c r="A148" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="149" spans="1:1">
-      <c r="A149" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="150" spans="1:1">
-      <c r="A150" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="151" spans="1:1">
-      <c r="A151" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="152" spans="1:1">
-      <c r="A152" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="153" spans="1:1">
-      <c r="A153" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="154" spans="1:1">
-      <c r="A154" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="155" spans="1:1">
-      <c r="A155" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="156" spans="1:1">
-      <c r="A156" t="s">
-        <v>155</v>
-      </c>
-    </row>
-    <row r="157" spans="1:1">
-      <c r="A157" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="158" spans="1:1">
-      <c r="A158" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="159" spans="1:1">
-      <c r="A159" t="s">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="160" spans="1:1">
-      <c r="A160" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="161" spans="1:1">
-      <c r="A161" t="s">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="162" spans="1:1">
-      <c r="A162" t="s">
-        <v>161</v>
-      </c>
-    </row>
-    <row r="163" spans="1:1">
-      <c r="A163" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="164" spans="1:1">
-      <c r="A164" t="s">
-        <v>163</v>
-      </c>
-    </row>
-    <row r="165" spans="1:1">
-      <c r="A165" t="s">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="166" spans="1:1">
-      <c r="A166" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="167" spans="1:1">
-      <c r="A167" t="s">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="168" spans="1:1">
-      <c r="A168" t="s">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="169" spans="1:1">
-      <c r="A169" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="170" spans="1:1">
-      <c r="A170" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="171" spans="1:1">
-      <c r="A171" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="172" spans="1:1">
-      <c r="A172" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="173" spans="1:1">
-      <c r="A173" t="s">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="174" spans="1:1">
-      <c r="A174" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="175" spans="1:1">
-      <c r="A175" t="s">
-        <v>174</v>
-      </c>
-    </row>
-    <row r="176" spans="1:1">
-      <c r="A176" t="s">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="177" spans="1:1">
-      <c r="A177" t="s">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="178" spans="1:1">
-      <c r="A178" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="179" spans="1:1">
-      <c r="A179" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="180" spans="1:1">
-      <c r="A180" t="s">
-        <v>179</v>
-      </c>
-    </row>
-    <row r="181" spans="1:1">
-      <c r="A181" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="182" spans="1:1">
-      <c r="A182" t="s">
-        <v>181</v>
-      </c>
-    </row>
-    <row r="183" spans="1:1">
-      <c r="A183" t="s">
-        <v>182</v>
-      </c>
-    </row>
-    <row r="184" spans="1:1">
-      <c r="A184" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="185" spans="1:1">
-      <c r="A185" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="186" spans="1:1">
-      <c r="A186" t="s">
-        <v>185</v>
-      </c>
-    </row>
-    <row r="187" spans="1:1">
-      <c r="A187" t="s">
-        <v>186</v>
-      </c>
-    </row>
-    <row r="188" spans="1:1">
-      <c r="A188" t="s">
-        <v>187</v>
-      </c>
-    </row>
-    <row r="189" spans="1:1">
-      <c r="A189" t="s">
-        <v>188</v>
-      </c>
-    </row>
-    <row r="190" spans="1:1">
-      <c r="A190" t="s">
-        <v>189</v>
-      </c>
-    </row>
-    <row r="191" spans="1:1">
-      <c r="A191" t="s">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="192" spans="1:1">
-      <c r="A192" t="s">
-        <v>191</v>
-      </c>
-    </row>
-    <row r="193" spans="1:1">
-      <c r="A193" t="s">
-        <v>192</v>
-      </c>
-    </row>
-    <row r="194" spans="1:1">
-      <c r="A194" t="s">
-        <v>193</v>
-      </c>
-    </row>
-    <row r="195" spans="1:1">
-      <c r="A195" t="s">
-        <v>194</v>
-      </c>
-    </row>
-    <row r="196" spans="1:1">
-      <c r="A196" t="s">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="197" spans="1:1">
-      <c r="A197" t="s">
-        <v>196</v>
-      </c>
-    </row>
-    <row r="198" spans="1:1">
-      <c r="A198" t="s">
-        <v>197</v>
-      </c>
-    </row>
-    <row r="199" spans="1:1">
-      <c r="A199" t="s">
-        <v>198</v>
-      </c>
-    </row>
-    <row r="200" spans="1:1">
-      <c r="A200" t="s">
-        <v>199</v>
-      </c>
-    </row>
-    <row r="201" spans="1:1">
-      <c r="A201" t="s">
-        <v>200</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
